--- a/DeptCount.xlsx
+++ b/DeptCount.xlsx
@@ -1,46 +1,53 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidgerbing/Documents/000/553/R_Part_1_2/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5B30D81-F2A5-504C-85A0-2364A38011FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25880" windowHeight="14480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="df" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="df" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
-    <t xml:space="preserve">Dept</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Freq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACCT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADMN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FINC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MKTG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SALE</t>
+    <t>Dept</t>
+  </si>
+  <si>
+    <t>ACCT</t>
+  </si>
+  <si>
+    <t>ADMN</t>
+  </si>
+  <si>
+    <t>FINC</t>
+  </si>
+  <si>
+    <t>MKTG</t>
+  </si>
+  <si>
+    <t>SALE</t>
+  </si>
+  <si>
+    <t>n</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -52,6 +59,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -76,22 +89,41 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -373,64 +405,63 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="4.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="4.71" hidden="0" customWidth="1"/>
+    <col min="1" max="2" width="4.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
+      <c r="B2" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>